--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_624_Guinea_Bissau.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_624_Guinea_Bissau.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf0bd3fd7ab7146bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R5d5a048c26c14aab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R475490cfab604391"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R8aacc69c472d4227"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R885cd68a5b304650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R16c28ddc09e94769"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R988ba4410a894a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rbc791510b5ef4d6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R626c5e7c37c44bda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R16fdbace4c35429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R17d1e9df6a034b56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2d9d1b3516d24cd7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ624CommercialTable" displayName="EEZ624CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ624CommercialTable" displayName="EEZ624CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ624FunctionalTable" displayName="EEZ624FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ624FunctionalTable" displayName="EEZ624FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ624ValidationTable" displayName="EEZ624ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ624ValidationTable" displayName="EEZ624ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -16037,7 +15991,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R495be6cd6b1f4b77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb532548decb49ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16047,20 +16001,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -16068,660 +16012,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>52.529000159599995</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>52.529000159599995</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$230,A2,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>6767.0460906493245</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>6767.0460906493245</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2534.9717594143003</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.420183004942669</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2631.3765794886012</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2534.9717594143003</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2841.9692688721457</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$230,A3,'Species'!$U$2:$U$230))</x:f>
-        <x:v>7204311.837714196</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.420183004942669</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2631.3765794886012</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>6670465.3173878025</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>533846.5203263937</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0800313763621294</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.08003137636212933</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1603.2712868764</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.199514884142515</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>158.31238226037573</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1603.2712868764</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>178.71657648064874</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$230,A4,'Species'!$U$2:$U$230))</x:f>
-        <x:v>286531.15556027426</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.199514884142515</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>158.31238226037573</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>253817.69683506113</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>32713.45872521313</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1288856495552846</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.1288856495552845</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>47274.23528376479</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.5253447434689615</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>335.2314406783825</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>47274.23528376479</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>346.49458084574627</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$230,A5,'Species'!$U$2:$U$230))</x:f>
-        <x:v>16380266.33945127</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.5253447434689615</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>335.2314406783825</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>15847810.001145294</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>532456.3383059762</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0335981020890266</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.033598102089026596</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>24829.5706282887</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.832529891910557</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>68.00328491475354</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>24829.5706282887</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>93.13333511466965</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$230,A6,'Species'!$U$2:$U$230))</x:f>
-        <x:v>2312460.72207777</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.832529891910557</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>68.00328491475354</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1688492.3657465125</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>623968.3563312576</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.3695417101014786</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.3695417101014787</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>9101.076104211501</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.033096582695222</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.791866957385679</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>9101.076104211501</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>11.249148951536261</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$230,A7,'Species'!$U$2:$U$230))</x:f>
-        <x:v>102379.36071554253</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.033096582695222</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.791866957385679</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>98217.60248569248</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4161.758229850049</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0423728346500445</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.04237283465004452</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>682933.2960532362</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3357951936468537</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>216.66820911279967</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>682933.2960532362</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>264.8528884495915</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$230,A8,'Species'!$U$2:$U$230))</x:f>
-        <x:v>180876856.0780996</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3357951936468537</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>216.66820911279967</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>147969934.1993561</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>32906921.8787435</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2223892445232072</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.2223892445232073</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>345005.84673590277</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.736264040298324</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>544.8337976352806</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>345005.84673590277</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>807.7651988922399</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$230,A9,'Species'!$U$2:$U$230))</x:f>
-        <x:v>278683716.40761214</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.736264040298324</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>544.8337976352806</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>187970845.6834975</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>90712870.72411466</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.4825901080258779</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.48259010802587776</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>972.9343746182</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8224383862033675</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>664.4134052203889</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>972.9343746182</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>673.9376505970846</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$230,A10,'Species'!$U$2:$U$230))</x:f>
-        <x:v>655697.1066153335</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8224383862033675</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>664.4134052203889</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>646430.6408960477</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>9266.46571928577</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0143348182048442</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.014334818204844203</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>15983.4182644897</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.602381315767192</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>4002.9606025607527</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>15983.4182644897</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>5544.388675197424</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$230,A11,'Species'!$U$2:$U$230))</x:f>
-        <x:v>88618283.21658036</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.602381315767192</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>4002.9606025607527</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>63980993.60700223</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>24637289.609578133</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.385072006866767</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.3850720068667669</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>3646.7110686251</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.374083718152148</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2366.3758154552975</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>3646.7110686251</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2408.443294143863</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$230,A12,'Species'!$U$2:$U$230))</x:f>
-        <x:v>8782896.818910323</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.374083718152148</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2366.3758154552975</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>8629488.87874758</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>153407.9401627425</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0177771757190104</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.017777175719010486</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red9f97baa0d04e24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37701e82717242a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16731,20 +16246,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -16752,1416 +16257,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>43928.66250035471</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.699152798004352</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>500.2104932828899</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>43928.66250035471</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>504.3322106466672</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$230,A2,'Species'!$U$2:$U$230))</x:f>
-        <x:v>22154639.46955524</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.699152798004352</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>500.2104932828899</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>21973577.938560016</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>181061.53099522367</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0082399658126449</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.008239965812644943</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1.5113541818</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.14</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1380.3842646028838</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1.5113541818</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$230,A3,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2086.2495307984864</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.14</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>2086.2495307984864</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3.1292459573</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3.1292459573</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$230,A4,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>6846.044217280219</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>6846.044217280219</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>49915.5648360705</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.350655298883664</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2242.101653102303</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>49915.5648360705</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2362.3579738926264</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$230,A5,'Species'!$U$2:$U$230))</x:f>
-        <x:v>117918432.61184554</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.350655298883664</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2242.101653102303</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>111915770.43448885</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>6002662.17735669</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0536355345993924</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.05363553459939246</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>41031.4058254186</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.7938427331186095</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>622.0749783520232</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>41031.4058254186</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>623.6897936495179</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$230,A6,'Species'!$U$2:$U$230))</x:f>
-        <x:v>25590869.032404955</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.7938427331186095</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>622.0749783520232</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>25524610.890600357</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>66258.14180459827</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.002595853158686</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0025958531586860885</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>78402.36942538146</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.997906228728865</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>995.1905162670507</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>78402.36942538146</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1062.9831716905712</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$230,A7,'Species'!$U$2:$U$230))</x:f>
-        <x:v>83340399.31984785</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.997906228728865</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>995.1905162670507</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>78025294.5050054</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>5315104.814842448</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0681202787962751</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0681202787962752</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>56.97201349930001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.434364994447441</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>271.87232076072894</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>56.97201349930001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>294.7013190332882</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$230,A8,'Species'!$U$2:$U$230))</x:f>
-        <x:v>16789.727526226015</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.434364994447441</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>271.87232076072894</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>15489.113528466272</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1300.6139977597431</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.083969556770918</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.08396955677091802</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2414.1429236002996</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.027123643883644</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1064.446023471891</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2414.1429236002996</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1193.4209884146737</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$230,A9,'Species'!$U$2:$U$230))</x:f>
-        <x:v>2881088.83405736</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.027123643883644</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1064.446023471891</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2569724.835119144</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>311363.9989382159</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1211662800168174</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.12116628001681731</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>14786.5165682213</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.668713055631427</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>4663.511538458288</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>14786.5165682213</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>5943.357799505584</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$230,A10,'Species'!$U$2:$U$230))</x:f>
-        <x:v>87881558.5732566</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.668713055631427</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>4663.511538458288</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>68957090.62950467</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>18924467.94375193</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2744383176696077</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.27443831766960775</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>34.462338397500005</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.066288238764138</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>116.48989096489146</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>34.462338397500005</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>130.7987656583537</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$230,A11,'Species'!$U$2:$U$230))</x:f>
-        <x:v>4507.631324093488</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.066288238764138</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>116.48989096489146</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>4014.5140423199678</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>493.11728177352006</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.122833617363199</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.12283361736319896</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>384.85194108289994</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.440837052878274</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2759.542282761373</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>384.85194108289994</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2945.970845361719</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$230,A12,'Species'!$U$2:$U$230))</x:f>
-        <x:v>1133762.5982110891</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.440837052878274</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2759.542282761373</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1062015.204021051</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>71747.39419003809</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0675577844068378</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.06755778440683785</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>204.3423538882</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.081272659815593</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1205.7927264991072</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>204.3423538882</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1206.5766176315203</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$230,A13,'Species'!$U$2:$U$230))</x:f>
-        <x:v>246554.70619328748</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.081272659815593</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1205.7927264991072</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>246394.5240340981</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>160.18215918936767</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0006501043796217</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0006501043796216849</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>21003.6797507964</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.9188122598298754</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>829.492110747655</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>21003.6797507964</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1568.2596619790247</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$230,A14,'Species'!$U$2:$U$230))</x:f>
-        <x:v>32939223.706299648</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.9188122598298754</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>829.492110747655</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>17422386.649955887</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>15516837.05634376</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.8906263744515766</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.8906263744515766</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>672103.2189754854</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.3091408411875123</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>203.77027951746132</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>672103.2189754854</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>216.88848535063053</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$230,A15,'Species'!$U$2:$U$230))</x:f>
-        <x:v>145771449.1628762</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.3091408411875123</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>203.77027951746132</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>136954660.79522017</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>8816788.367656022</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0643774247364917</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.06437742473649159</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>91804.8416262851</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.455149411994274</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>285.19992829815385</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>91804.8416262851</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>368.16501753511216</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$230,A16,'Species'!$U$2:$U$230))</x:f>
-        <x:v>33799331.12714945</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.455149411994274</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>285.19992829815385</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>26182734.24923988</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>7616596.877909567</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.2909015080474526</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.2909015080474526</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>7136.5242928005</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.4885899202513175</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>308.0278044064165</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>7136.5242928005</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>576.5357196349947</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$230,A17,'Species'!$U$2:$U$230))</x:f>
-        <x:v>4114461.168842358</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.4885899202513175</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>308.0278044064165</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2198247.9090043926</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>1916213.2598379655</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.871700253637833</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.8717002536378332</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>9101.0937991356</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.0330973543800326</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>10.791886133146726</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>9101.0937991356</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>11.249179410754671</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$230,A18,'Species'!$U$2:$U$230))</x:f>
-        <x:v>102379.8369805832</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.0330973543800326</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>10.791886133146726</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>98217.96796735913</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>4161.869013224074</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0423738049091709</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.04237380490917091</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>1568.8089484789</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.2024415003764704</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>159.38281770212575</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>1568.8089484789</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>179.76919656764304</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$230,A19,'Species'!$U$2:$U$230))</x:f>
-        <x:v>282023.52423618076</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.2024415003764704</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>159.38281770212575</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>250041.1906448761</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>31982.33359130466</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1279082598703825</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.12790825987038248</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>140.2461063628</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.19</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>154.88166189124811</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>140.2461063628</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>154.88166189124811</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$230,A20,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>21721.55002724721</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.19</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>154.88166189124811</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>21721.55002724721</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>43875.62143855869</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.0947639138374288</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>124.38382669267378</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>43875.62143855869</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>174.64328981018554</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$230,A21,'Species'!$U$2:$U$230))</x:f>
-        <x:v>7662582.870496196</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.0947639138374288</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>124.38382669267378</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>5457417.693047047</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>2205165.177449149</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.4040675098515203</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.40406750985152035</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>7624.5281208654005</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>2.982493827374885</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>96.04921668197599</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>7624.5281208654005</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>123.10427444263681</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$230,A22,'Species'!$U$2:$U$230))</x:f>
-        <x:v>938612.0022866161</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>2.982493827374885</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>96.04921668197599</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>732329.9535788201</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>206282.04870779603</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.2816791088493884</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.2816791088493884</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>1.2012082306999998</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.73</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>537.0317963702527</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>1.2012082306999998</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$230,A23,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>645.0870139475538</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>645.0870139475538</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>47274.23528376479</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.5253447434689615</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>335.2314406783825</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>47274.23528376479</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>346.49458084574627</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$230,A24,'Species'!$U$2:$U$230))</x:f>
-        <x:v>16380266.33945127</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.5253447434689615</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>335.2314406783825</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>15847810.001145294</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>532456.3383059762</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0335981020890266</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.033598102089026596</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>1137.6332926209</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.8000000000000003</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>630.9573444801937</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>1137.6332926209</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$230,A25,'Species'!$U$2:$U$230))</x:f>
-        <x:v>717798.0813043414</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.8000000000000003</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>630.9573444801937</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>717798.0813043421</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>-6.984919309616089e-10</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>-9.731036473270433e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>2.2963901482</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.9685906320519897</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>930.2306224784536</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>2.2963901482</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>930.518925479652</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$230,A26,'Species'!$U$2:$U$230))</x:f>
-        <x:v>2136.834493185123</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.9685906320519897</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>930.2306224784536</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>2136.1724370134743</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>0.6620561716486009</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.000309926371194</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.0003099263711941738</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0d78b7d4c0845a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6e70d62ed084fb6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18336,7 +16922,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -18435,7 +17021,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>583910166.0894275</x:v>
+        <x:v>433763263.03919053</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18449,7 +17035,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>583910166.0894275</x:v>
+        <x:v>516189062.1832388</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18463,7 +17049,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-150146903.05023694</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18477,7 +17063,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-67721103.90618867</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18488,9 +17074,9 @@
         <x:v>EEZ_624</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -18502,47 +17088,19 @@
         <x:v>EEZ_624</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_624</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_624</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f223150539d49c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R679c60a1380d448d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18589,7 +17147,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
